--- a/output_phyto/phyto_Intermediate_jasper_1990.xlsx
+++ b/output_phyto/phyto_Intermediate_jasper_1990.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
   <si>
     <t>NA</t>
   </si>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_1</t>
+    <t xml:space="preserve">96-619-1-1,58-63</t>
   </si>
   <si>
     <t xml:space="preserve">10.1038/347462a0</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_jasper_1990.xlsx</t>
+    <t xml:space="preserve">phytoplankton_jasper_1990_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,157 +1475,94 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">assumed</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">d13C_foram was estimated graphically using WebPlotDigitizer. pCO2 was estimated graphically using WebPlotDigitizer. pCO2 uncertainty was approximated graphically using WebPlotDigitizer. Sample information obtained by comparison with Jasper and Gagosian (1989).</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Zhang_2019_80</t>
+    <t xml:space="preserve">96-619-1-2,9-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-1-3,45-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-1-4,45-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-1-4,131-136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-1-5,76-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-4-1,10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-4-2,130-135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-4-5,85-90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-4CC,10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-5-2,90-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-5CC,5-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-7-2,113-118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-8CC,2-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-11-2,5-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-13-2,5-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-13-4,123-128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-14-2,5-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-15-2,5-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-16-2,5-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alkenone unsaturation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-17-2,8-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-17-2,116-121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-17-3,76-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-17-4,12-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-18-1,45-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-18CC,0-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-19-1,47-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96-619-22-1,50-55</t>
   </si>
 </sst>
 </file>
@@ -1633,7 +1570,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1699,12 +1636,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1818,7 +1749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1917,7 +1848,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2643,7 +2573,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2661,8 +2591,8 @@
       <c r="H5" t="n">
         <v>0.0018</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2679,8 +2609,8 @@
       <c r="N5" t="n">
         <v>-22.7316709410784</v>
       </c>
-      <c r="O5" t="e">
-        <v>#N/A</v>
+      <c r="O5" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2689,10 +2619,10 @@
         <v>#N/A</v>
       </c>
       <c r="R5" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+        <v>24.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2718,20 +2648,20 @@
       <c r="AA5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2753,7 +2683,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2771,8 +2701,8 @@
       <c r="H6" t="n">
         <v>0.0029</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2789,8 +2719,8 @@
       <c r="N6" t="n">
         <v>-26.7514595618863</v>
       </c>
-      <c r="O6" t="e">
-        <v>#N/A</v>
+      <c r="O6" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2799,10 +2729,10 @@
         <v>#N/A</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+        <v>25.6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2828,26 +2758,26 @@
       <c r="AA6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH6" t="s">
-        <v>280</v>
+      <c r="AH6" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI6" t="e">
         <v>#N/A</v>
@@ -2858,12 +2788,12 @@
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2881,8 +2811,8 @@
       <c r="H7" t="n">
         <v>0.00489</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2899,8 +2829,8 @@
       <c r="N7" t="n">
         <v>-23.9993710897299</v>
       </c>
-      <c r="O7" t="e">
-        <v>#N/A</v>
+      <c r="O7" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2909,10 +2839,10 @@
         <v>#N/A</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+        <v>22.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2938,20 +2868,20 @@
       <c r="AA7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -2968,12 +2898,12 @@
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2991,8 +2921,8 @@
       <c r="H8" t="n">
         <v>0.0065</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3009,8 +2939,8 @@
       <c r="N8" t="n">
         <v>-23.5933923583318</v>
       </c>
-      <c r="O8" t="e">
-        <v>#N/A</v>
+      <c r="O8" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3019,10 +2949,10 @@
         <v>#N/A</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+        <v>20.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3048,20 +2978,20 @@
       <c r="AA8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3078,12 +3008,12 @@
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3101,8 +3031,8 @@
       <c r="H9" t="n">
         <v>0.0075</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3119,8 +3049,8 @@
       <c r="N9" t="n">
         <v>-23.3903458189718</v>
       </c>
-      <c r="O9" t="e">
-        <v>#N/A</v>
+      <c r="O9" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3129,10 +3059,10 @@
         <v>#N/A</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+        <v>19.9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3158,20 +3088,20 @@
       <c r="AA9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3188,12 +3118,12 @@
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3211,8 +3141,8 @@
       <c r="H10" t="n">
         <v>0.0085</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3229,8 +3159,8 @@
       <c r="N10" t="n">
         <v>-25.9645212931048</v>
       </c>
-      <c r="O10" t="e">
-        <v>#N/A</v>
+      <c r="O10" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3239,10 +3169,10 @@
         <v>#N/A</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+        <v>20.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3268,26 +3198,26 @@
       <c r="AA10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH10" t="s">
-        <v>285</v>
+      <c r="AH10" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI10" t="e">
         <v>#N/A</v>
@@ -3298,12 +3228,12 @@
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3321,8 +3251,8 @@
       <c r="H11" t="n">
         <v>0.0151</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3339,8 +3269,8 @@
       <c r="N11" t="n">
         <v>-26.4328879232892</v>
       </c>
-      <c r="O11" t="e">
-        <v>#N/A</v>
+      <c r="O11" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3349,10 +3279,10 @@
         <v>#N/A</v>
       </c>
       <c r="R11" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+        <v>18.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3378,26 +3308,26 @@
       <c r="AA11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH11" t="s">
-        <v>287</v>
+      <c r="AH11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI11" t="e">
         <v>#N/A</v>
@@ -3408,12 +3338,12 @@
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3431,8 +3361,8 @@
       <c r="H12" t="n">
         <v>0.016</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3449,8 +3379,8 @@
       <c r="N12" t="n">
         <v>-24.3657399088488</v>
       </c>
-      <c r="O12" t="e">
-        <v>#N/A</v>
+      <c r="O12" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3459,10 +3389,10 @@
         <v>#N/A</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+        <v>21.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3488,26 +3418,26 @@
       <c r="AA12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH12" t="s">
-        <v>289</v>
+      <c r="AH12" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI12" t="e">
         <v>#N/A</v>
@@ -3518,12 +3448,12 @@
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3541,8 +3471,8 @@
       <c r="H13" t="n">
         <v>0.0174</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3559,8 +3489,8 @@
       <c r="N13" t="n">
         <v>-23.8836630347779</v>
       </c>
-      <c r="O13" t="e">
-        <v>#N/A</v>
+      <c r="O13" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3569,10 +3499,10 @@
         <v>#N/A</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+        <v>18.7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3598,26 +3528,26 @@
       <c r="AA13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH13" t="s">
-        <v>291</v>
+      <c r="AH13" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI13" t="e">
         <v>#N/A</v>
@@ -3628,12 +3558,12 @@
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3651,8 +3581,8 @@
       <c r="H14" t="n">
         <v>0.0178</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3669,8 +3599,8 @@
       <c r="N14" t="n">
         <v>-24.5684091020468</v>
       </c>
-      <c r="O14" t="e">
-        <v>#N/A</v>
+      <c r="O14" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3679,10 +3609,10 @@
         <v>#N/A</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+        <v>1.8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3708,26 +3638,26 @@
       <c r="AA14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH14" t="s">
-        <v>293</v>
+      <c r="AH14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI14" t="e">
         <v>#N/A</v>
@@ -3738,12 +3668,12 @@
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3761,8 +3691,8 @@
       <c r="H15" t="n">
         <v>0.0191</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3779,8 +3709,8 @@
       <c r="N15" t="n">
         <v>-21.4106048973324</v>
       </c>
-      <c r="O15" t="e">
-        <v>#N/A</v>
+      <c r="O15" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3789,10 +3719,10 @@
         <v>#N/A</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+        <v>18.9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3818,26 +3748,26 @@
       <c r="AA15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH15" t="s">
-        <v>295</v>
+      <c r="AH15" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI15" t="e">
         <v>#N/A</v>
@@ -3848,12 +3778,12 @@
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3871,8 +3801,8 @@
       <c r="H16" t="n">
         <v>0.0206</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3889,8 +3819,8 @@
       <c r="N16" t="n">
         <v>-25.93761536828</v>
       </c>
-      <c r="O16" t="e">
-        <v>#N/A</v>
+      <c r="O16" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3899,10 +3829,10 @@
         <v>#N/A</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+        <v>19.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3928,20 +3858,20 @@
       <c r="AA16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -3958,12 +3888,12 @@
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3981,8 +3911,8 @@
       <c r="H17" t="n">
         <v>0.0267</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3999,8 +3929,8 @@
       <c r="N17" t="n">
         <v>-23.4640083636898</v>
       </c>
-      <c r="O17" t="e">
-        <v>#N/A</v>
+      <c r="O17" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4009,10 +3939,10 @@
         <v>#N/A</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+        <v>19.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4038,26 +3968,26 @@
       <c r="AA17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH17" t="s">
-        <v>298</v>
+      <c r="AH17" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI17" t="e">
         <v>#N/A</v>
@@ -4068,12 +3998,12 @@
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4091,8 +4021,8 @@
       <c r="H18" t="n">
         <v>0.0339</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4109,8 +4039,8 @@
       <c r="N18" t="n">
         <v>-23.9576571867291</v>
       </c>
-      <c r="O18" t="e">
-        <v>#N/A</v>
+      <c r="O18" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4119,10 +4049,10 @@
         <v>#N/A</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S18" t="e">
-        <v>#N/A</v>
+        <v>18.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4148,26 +4078,26 @@
       <c r="AA18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH18" t="s">
-        <v>300</v>
+      <c r="AH18" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI18" t="e">
         <v>#N/A</v>
@@ -4178,12 +4108,12 @@
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4201,8 +4131,8 @@
       <c r="H19" t="n">
         <v>0.0462</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4219,8 +4149,8 @@
       <c r="N19" t="n">
         <v>-23.4615498962706</v>
       </c>
-      <c r="O19" t="e">
-        <v>#N/A</v>
+      <c r="O19" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4229,10 +4159,10 @@
         <v>#N/A</v>
       </c>
       <c r="R19" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S19" t="e">
-        <v>#N/A</v>
+        <v>2.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4258,26 +4188,26 @@
       <c r="AA19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH19" t="s">
-        <v>302</v>
+      <c r="AH19" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI19" t="e">
         <v>#N/A</v>
@@ -4288,12 +4218,12 @@
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4311,8 +4241,8 @@
       <c r="H20" t="n">
         <v>0.0573</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4329,8 +4259,8 @@
       <c r="N20" t="n">
         <v>-24.3604913667771</v>
       </c>
-      <c r="O20" t="e">
-        <v>#N/A</v>
+      <c r="O20" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4339,10 +4269,10 @@
         <v>#N/A</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S20" t="e">
-        <v>#N/A</v>
+        <v>20.8</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4368,26 +4298,26 @@
       <c r="AA20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH20" t="s">
-        <v>304</v>
+      <c r="AH20" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI20" t="e">
         <v>#N/A</v>
@@ -4398,12 +4328,12 @@
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4421,8 +4351,8 @@
       <c r="H21" t="n">
         <v>0.0601</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4439,8 +4369,8 @@
       <c r="N21" t="n">
         <v>-22.8637649672476</v>
       </c>
-      <c r="O21" t="e">
-        <v>#N/A</v>
+      <c r="O21" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4449,10 +4379,10 @@
         <v>#N/A</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S21" t="e">
-        <v>#N/A</v>
+        <v>19.8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4478,26 +4408,26 @@
       <c r="AA21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH21" t="s">
-        <v>306</v>
+      <c r="AH21" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI21" t="e">
         <v>#N/A</v>
@@ -4508,12 +4438,12 @@
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4531,8 +4461,8 @@
       <c r="H22" t="n">
         <v>0.0618</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4549,8 +4479,8 @@
       <c r="N22" t="n">
         <v>-24.8925380204844</v>
       </c>
-      <c r="O22" t="e">
-        <v>#N/A</v>
+      <c r="O22" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4559,10 +4489,10 @@
         <v>#N/A</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S22" t="e">
-        <v>#N/A</v>
+        <v>17.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4588,26 +4518,26 @@
       <c r="AA22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH22" t="s">
-        <v>308</v>
+      <c r="AH22" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI22" t="e">
         <v>#N/A</v>
@@ -4618,12 +4548,12 @@
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4641,8 +4571,8 @@
       <c r="H23" t="n">
         <v>0.0659</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4659,8 +4589,8 @@
       <c r="N23" t="n">
         <v>-24.7652122776352</v>
       </c>
-      <c r="O23" t="e">
-        <v>#N/A</v>
+      <c r="O23" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4669,10 +4599,10 @@
         <v>#N/A</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S23" t="e">
-        <v>#N/A</v>
+        <v>22.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4698,26 +4628,26 @@
       <c r="AA23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH23" t="s">
-        <v>310</v>
+      <c r="AH23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI23" t="e">
         <v>#N/A</v>
@@ -4728,12 +4658,12 @@
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4751,8 +4681,8 @@
       <c r="H24" t="n">
         <v>0.072</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4769,8 +4699,8 @@
       <c r="N24" t="n">
         <v>-23.3060947122531</v>
       </c>
-      <c r="O24" t="e">
-        <v>#N/A</v>
+      <c r="O24" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4778,8 +4708,8 @@
       <c r="Q24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="R24" s="11" t="n">
-        <v>23</v>
+      <c r="R24" s="11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="S24" t="e">
         <v>#N/A</v>
@@ -4791,7 +4721,7 @@
         <v>#N/A</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="W24" t="e">
         <v>#N/A</v>
@@ -4808,26 +4738,26 @@
       <c r="AA24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH24" t="s">
-        <v>312</v>
+      <c r="AH24" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI24" t="e">
         <v>#N/A</v>
@@ -4838,12 +4768,12 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4861,8 +4791,8 @@
       <c r="H25" t="n">
         <v>0.0802</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4879,8 +4809,8 @@
       <c r="N25" t="n">
         <v>-24.8394579936945</v>
       </c>
-      <c r="O25" t="e">
-        <v>#N/A</v>
+      <c r="O25" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4889,10 +4819,10 @@
         <v>#N/A</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S25" t="e">
-        <v>#N/A</v>
+        <v>24.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4918,26 +4848,26 @@
       <c r="AA25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH25" t="s">
-        <v>314</v>
+      <c r="AH25" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI25" t="e">
         <v>#N/A</v>
@@ -4948,12 +4878,12 @@
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4971,8 +4901,8 @@
       <c r="H26" t="n">
         <v>0.0815</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4989,8 +4919,8 @@
       <c r="N26" t="n">
         <v>-24.1418364179884</v>
       </c>
-      <c r="O26" t="e">
-        <v>#N/A</v>
+      <c r="O26" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4999,10 +4929,10 @@
         <v>#N/A</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S26" t="e">
-        <v>#N/A</v>
+        <v>24.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5028,26 +4958,26 @@
       <c r="AA26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH26" t="s">
-        <v>316</v>
+      <c r="AH26" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI26" t="e">
         <v>#N/A</v>
@@ -5058,12 +4988,12 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5081,8 +5011,8 @@
       <c r="H27" t="n">
         <v>0.0829</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5099,8 +5029,8 @@
       <c r="N27" t="n">
         <v>-24.0655667543329</v>
       </c>
-      <c r="O27" t="e">
-        <v>#N/A</v>
+      <c r="O27" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5108,8 +5038,8 @@
       <c r="Q27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>23</v>
+      <c r="R27" s="11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="S27" t="e">
         <v>#N/A</v>
@@ -5121,7 +5051,7 @@
         <v>#N/A</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="W27" t="e">
         <v>#N/A</v>
@@ -5138,26 +5068,26 @@
       <c r="AA27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH27" t="s">
-        <v>318</v>
+      <c r="AH27" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI27" t="e">
         <v>#N/A</v>
@@ -5168,12 +5098,12 @@
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5191,8 +5121,8 @@
       <c r="H28" t="n">
         <v>0.0918</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5209,8 +5139,8 @@
       <c r="N28" t="n">
         <v>-23.4303673816096</v>
       </c>
-      <c r="O28" t="e">
-        <v>#N/A</v>
+      <c r="O28" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5218,8 +5148,8 @@
       <c r="Q28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="R28" s="11" t="n">
-        <v>23</v>
+      <c r="R28" s="11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="S28" t="e">
         <v>#N/A</v>
@@ -5231,7 +5161,7 @@
         <v>#N/A</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="W28" t="e">
         <v>#N/A</v>
@@ -5248,26 +5178,26 @@
       <c r="AA28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH28" t="s">
-        <v>320</v>
+      <c r="AH28" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI28" t="e">
         <v>#N/A</v>
@@ -5278,12 +5208,12 @@
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5301,8 +5231,8 @@
       <c r="H29" t="n">
         <v>0.09311</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5319,8 +5249,8 @@
       <c r="N29" t="n">
         <v>-24.3686328960909</v>
       </c>
-      <c r="O29" t="e">
-        <v>#N/A</v>
+      <c r="O29" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5328,8 +5258,8 @@
       <c r="Q29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="R29" s="11" t="n">
-        <v>23</v>
+      <c r="R29" s="11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="S29" t="e">
         <v>#N/A</v>
@@ -5341,7 +5271,7 @@
         <v>#N/A</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="W29" t="e">
         <v>#N/A</v>
@@ -5358,26 +5288,26 @@
       <c r="AA29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH29" t="s">
-        <v>322</v>
+      <c r="AH29" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI29" t="e">
         <v>#N/A</v>
@@ -5388,12 +5318,12 @@
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5411,8 +5341,8 @@
       <c r="H30" t="n">
         <v>0.0932</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5429,8 +5359,8 @@
       <c r="N30" t="n">
         <v>-24.1910629400329</v>
       </c>
-      <c r="O30" t="e">
-        <v>#N/A</v>
+      <c r="O30" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5439,10 +5369,10 @@
         <v>#N/A</v>
       </c>
       <c r="R30" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S30" t="e">
-        <v>#N/A</v>
+        <v>21.7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5468,20 +5398,20 @@
       <c r="AA30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5498,12 +5428,12 @@
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5521,8 +5451,8 @@
       <c r="H31" t="n">
         <v>0.0939</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5539,8 +5469,8 @@
       <c r="N31" t="n">
         <v>-25.7888151983925</v>
       </c>
-      <c r="O31" t="e">
-        <v>#N/A</v>
+      <c r="O31" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5549,10 +5479,10 @@
         <v>#N/A</v>
       </c>
       <c r="R31" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S31" t="e">
-        <v>#N/A</v>
+        <v>23.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5578,26 +5508,26 @@
       <c r="AA31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH31" t="s">
-        <v>325</v>
+      <c r="AH31" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI31" t="e">
         <v>#N/A</v>
@@ -5608,12 +5538,12 @@
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5631,8 +5561,8 @@
       <c r="H32" t="n">
         <v>0.096</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5649,8 +5579,8 @@
       <c r="N32" t="n">
         <v>-25.7631899635722</v>
       </c>
-      <c r="O32" t="e">
-        <v>#N/A</v>
+      <c r="O32" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5659,10 +5589,10 @@
         <v>#N/A</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S32" t="e">
-        <v>#N/A</v>
+        <v>24.2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5688,26 +5618,26 @@
       <c r="AA32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AH32" t="s">
-        <v>327</v>
+      <c r="AH32" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AI32" t="e">
         <v>#N/A</v>
@@ -6018,36 +5948,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
